--- a/VerveStacks_GBR/SysSettings.xlsx
+++ b/VerveStacks_GBR/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCC9B23-2005-42AA-A1ED-3B9F6A70F721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8837D041-0715-4122-9727-42AC48A6F122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GBR/SysSettings.xlsx
+++ b/VerveStacks_GBR/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8837D041-0715-4122-9727-42AC48A6F122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9777635-B420-41AE-940E-0EBCCE96A22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GBR/SysSettings.xlsx
+++ b/VerveStacks_GBR/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9777635-B420-41AE-940E-0EBCCE96A22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B99BCA-1466-47A7-9F16-4A38D593BCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GBR/SysSettings.xlsx
+++ b/VerveStacks_GBR/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B99BCA-1466-47A7-9F16-4A38D593BCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFD6352-79AB-4B5C-876D-4BB2BEA534CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
